--- a/productos (1).xlsx
+++ b/productos (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>nombre</t>
   </si>
@@ -188,6 +188,9 @@
   </si>
   <si>
     <t>imagen28.jpg,imagen28a.jpg,imagen28b.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">llaveros plastico/resina </t>
   </si>
 </sst>
 </file>
@@ -821,7 +824,14 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="8">
+        <v>2500.0</v>
+      </c>
+    </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
